--- a/椙山改修/工程リンク.xlsx
+++ b/椙山改修/工程リンク.xlsx
@@ -1573,7 +1573,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>カウンター造作</t>
+          <t>カウンター下地取付</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -1584,9 +1584,9 @@
       <c r="G35" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>迷い：家具本体の取付として カウンター造作（2/15〜）に結びつけた。リストの 1/18 は カウンター下地取付（三友-12）と同じ日</t>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>1/18（2026/10/31 ユーザー確認）。三友-12 窓際カウンター下地と同じ工程</t>
         </is>
       </c>
     </row>
@@ -2576,6 +2576,7 @@
         </is>
       </c>
     </row>
+    <row r="65"/>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>

--- a/椙山改修/工程リンク.xlsx
+++ b/椙山改修/工程リンク.xlsx
@@ -2404,9 +2404,9 @@
       <c r="G59" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H59" s="6" t="inlineStr">
-        <is>
-          <t>迷い：モルタルアートを左官（浪花組）の最初の工程と見なした。床タイル下地モルタル（行50）なら 1/21</t>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>12/22（2026/10/31 ユーザー確認）。左官の最初の工程＝東側柱型モルタルアート</t>
         </is>
       </c>
     </row>

--- a/椙山改修/工程リンク.xlsx
+++ b/椙山改修/工程リンク.xlsx
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>既存天井開口塞ぎ・新設開口補強→ルーバー天井下地　300m2</t>
+          <t>天井ボード下地 300m2 80m2/日→4日</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2476,9 +2476,9 @@
       <c r="G61" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>迷い：ルーバー天井下地を LGS（ミルックス）の最初の工程と見なした。天井ボード下地（同じ行）なら 12/16</t>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>12/16（2026/10/31 ユーザー確認）。天井ボード下地に結びつけ</t>
         </is>
       </c>
     </row>

--- a/椙山改修/工程リンク.xlsx
+++ b/椙山改修/工程リンク.xlsx
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>天井ボード下地 300m2 80m2/日→4日</t>
+          <t>既存天井開口塞ぎ・新設開口補強→ルーバー天井下地　300m2</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>12/16（2026/10/31 ユーザー確認）。天井ボード下地に結びつけ</t>
+          <t>11/24（2026/10/31 ユーザー確認、12/16 から訂正）。LGS の最初の工程＝ルーバー天井下地</t>
         </is>
       </c>
     </row>

--- a/椙山改修/工程リンク.xlsx
+++ b/椙山改修/工程リンク.xlsx
@@ -2112,9 +2112,9 @@
       <c r="G51" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>迷い：アン・シティ（コンクリート工事と同じ業者）なので SSD下躯体のアンカーと見なした。下地鉄骨のアンカーなら 12/14（アルミルーバー下地）</t>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>1/6（2026/10/31 ユーザー確認）。SSD下躯体に合わせる</t>
         </is>
       </c>
     </row>

--- a/椙山改修/工程リンク.xlsx
+++ b/椙山改修/工程リンク.xlsx
@@ -2465,7 +2465,7 @@
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>既存天井開口塞ぎ・新設開口補強→ルーバー天井下地　300m2</t>
+          <t>天井ボード下地 300m2 80m2/日→4日</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>11/24（2026/10/31 ユーザー確認、12/16 から訂正）。LGS の最初の工程＝ルーバー天井下地</t>
+          <t>12/16（10/31 小山さん指示で 12/16 に戻す。11/24 ルーバー天井下地は取り消し）</t>
         </is>
       </c>
     </row>
